--- a/OUTPUT/reverse_Ex_4_Motif_3.xlsx
+++ b/OUTPUT/reverse_Ex_4_Motif_3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,18 +461,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[(10, 4), (11, 3), (12, 2), (13, 1)]</t>
+          <t>[(21, 4), (22, 3), (23, 2), (24, 1)]</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>3.333380727548378</v>
+        <v>6.537295830588036</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>TCTT</t>
+          <t>TTTT</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -487,23 +487,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[(10, 5), (11, 4), (12, 3), (13, 2)]</t>
+          <t>[(21, 3), (22, 2), (23, 1)]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>3.026747885108934</v>
+        <v>4.810017697466028</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>TCTT</t>
+          <t>TTT</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AAAA</t>
+          <t>AAA</t>
         </is>
       </c>
     </row>
@@ -513,23 +513,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[(21, 4), (22, 3), (23, 2), (24, 1)]</t>
+          <t>[(22, 4), (23, 3), (24, 2)]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>6.537295830588036</v>
+        <v>5.465997267182336</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>TTTT</t>
+          <t>TTT</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AAAA</t>
+          <t>AAA</t>
         </is>
       </c>
     </row>
@@ -539,18 +539,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[(10, 3), (11, 2), (12, 1)]</t>
+          <t>[(22, 5), (23, 4), (24, 3)]</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7947935380666</v>
+        <v>4.714632654341308</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TCT</t>
+          <t>TTT</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -565,23 +565,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[(15, 8), (16, 7), (17, 6)]</t>
+          <t>[(21, 2), (22, 1)]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>2.545601318490206</v>
+        <v>2.954344421441552</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>GTC</t>
+          <t>TT</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>GAG</t>
+          <t>AA</t>
         </is>
       </c>
     </row>
@@ -591,255 +591,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[(21, 3), (22, 2), (23, 1)]</t>
+          <t>[(23, 5), (24, 4)]</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>4.810017697466028</v>
+        <v>2.969563010918459</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>TTT</t>
+          <t>TT</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>[(22, 4), (23, 3), (24, 2)]</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D8" t="n">
-        <v>5.465997267182336</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>TTT</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>[(22, 5), (23, 4), (24, 3)]</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>3</v>
-      </c>
-      <c r="D9" t="n">
-        <v>4.714632654341308</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>TTT</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>[(10, 2), (11, 1)]</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" t="n">
-        <v>2.068274362357816</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>TC</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>[(12, 4), (13, 3)]</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1.394873732103306</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>TT</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>[(15, 6), (16, 5)]</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1.776213789674345</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>GT</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>GA</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>[(16, 9), (17, 8)]</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" t="n">
-        <v>2.037025478970011</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>TC</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>AG</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>[(20, 17), (21, 16)]</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1.55331137645271</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>GT</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>[(21, 2), (22, 1)]</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" t="n">
-        <v>2.954344421441552</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>TT</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>[(23, 5), (24, 4)]</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" t="n">
-        <v>2.969563010918459</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>TT</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
